--- a/week-01/Ex4C_GTrends_marketing.xlsx
+++ b/week-01/Ex4C_GTrends_marketing.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\coreyallen\Documents\DataAnalytics\week-01\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:9_{6772282C-AEE4-4DD4-BCBD-B7240BCACE01}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:9_{CD303116-897A-4161-B64E-4FC94C876D58}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="2" xr2:uid="{CACB87C4-AAB2-4395-8604-77BFD5D8EA7B}"/>
+    <workbookView xWindow="-90" yWindow="0" windowWidth="9780" windowHeight="11370" xr2:uid="{CACB87C4-AAB2-4395-8604-77BFD5D8EA7B}"/>
   </bookViews>
   <sheets>
     <sheet name="By Search Term" sheetId="1" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="154" uniqueCount="68">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="150" uniqueCount="67">
   <si>
     <t>Region</t>
   </si>
@@ -223,9 +223,6 @@
   </si>
   <si>
     <t>Grand Total</t>
-  </si>
-  <si>
-    <t>(All)</t>
   </si>
   <si>
     <t>Sum of Hamburger</t>
@@ -964,37 +961,25 @@
           <c:invertIfNegative val="0"/>
           <c:cat>
             <c:strRef>
-              <c:f>'Sales Region Lookup'!$A$16:$A$26</c:f>
+              <c:f>'Sales Region Lookup'!$A$16:$A$22</c:f>
               <c:strCache>
-                <c:ptCount val="10"/>
+                <c:ptCount val="6"/>
                 <c:pt idx="0">
-                  <c:v>Idaho</c:v>
+                  <c:v>Michigan</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>Michigan</c:v>
+                  <c:v>Minnesota</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>Minnesota</c:v>
+                  <c:v>Nebraska</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>Montana</c:v>
+                  <c:v>North Dakota</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>Nebraska</c:v>
+                  <c:v>South Dakota</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>North Dakota</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>Oregon</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>South Dakota</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>Washington</c:v>
-                </c:pt>
-                <c:pt idx="9">
                   <c:v>Wisconsin</c:v>
                 </c:pt>
               </c:strCache>
@@ -1002,38 +987,26 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'Sales Region Lookup'!$B$16:$B$26</c:f>
+              <c:f>'Sales Region Lookup'!$B$16:$B$22</c:f>
               <c:numCache>
                 <c:formatCode>0%</c:formatCode>
-                <c:ptCount val="10"/>
+                <c:ptCount val="6"/>
                 <c:pt idx="0">
                   <c:v>0.67</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0.67</c:v>
+                  <c:v>0.68</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0.68</c:v>
+                  <c:v>0.69</c:v>
                 </c:pt>
                 <c:pt idx="3">
+                  <c:v>0.7</c:v>
+                </c:pt>
+                <c:pt idx="4">
                   <c:v>0.75</c:v>
                 </c:pt>
-                <c:pt idx="4">
-                  <c:v>0.69</c:v>
-                </c:pt>
                 <c:pt idx="5">
-                  <c:v>0.7</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>0.69</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>0.75</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>0.68</c:v>
-                </c:pt>
-                <c:pt idx="9">
                   <c:v>0.66</c:v>
                 </c:pt>
               </c:numCache>
@@ -1071,37 +1044,25 @@
           <c:invertIfNegative val="0"/>
           <c:cat>
             <c:strRef>
-              <c:f>'Sales Region Lookup'!$A$16:$A$26</c:f>
+              <c:f>'Sales Region Lookup'!$A$16:$A$22</c:f>
               <c:strCache>
-                <c:ptCount val="10"/>
+                <c:ptCount val="6"/>
                 <c:pt idx="0">
-                  <c:v>Idaho</c:v>
+                  <c:v>Michigan</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>Michigan</c:v>
+                  <c:v>Minnesota</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>Minnesota</c:v>
+                  <c:v>Nebraska</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>Montana</c:v>
+                  <c:v>North Dakota</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>Nebraska</c:v>
+                  <c:v>South Dakota</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>North Dakota</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>Oregon</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>South Dakota</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>Washington</c:v>
-                </c:pt>
-                <c:pt idx="9">
                   <c:v>Wisconsin</c:v>
                 </c:pt>
               </c:strCache>
@@ -1109,38 +1070,26 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'Sales Region Lookup'!$C$16:$C$26</c:f>
+              <c:f>'Sales Region Lookup'!$C$16:$C$22</c:f>
               <c:numCache>
                 <c:formatCode>0%</c:formatCode>
-                <c:ptCount val="10"/>
+                <c:ptCount val="6"/>
                 <c:pt idx="0">
                   <c:v>0.2</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0.2</c:v>
+                  <c:v>0.19</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0.19</c:v>
+                  <c:v>0.18</c:v>
                 </c:pt>
                 <c:pt idx="3">
+                  <c:v>0.18</c:v>
+                </c:pt>
+                <c:pt idx="4">
                   <c:v>0.14000000000000001</c:v>
                 </c:pt>
-                <c:pt idx="4">
-                  <c:v>0.18</c:v>
-                </c:pt>
                 <c:pt idx="5">
-                  <c:v>0.18</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>0.17</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>0.14000000000000001</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>0.18</c:v>
-                </c:pt>
-                <c:pt idx="9">
                   <c:v>0.2</c:v>
                 </c:pt>
               </c:numCache>
@@ -2063,7 +2012,7 @@
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
 <pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{568B1B48-594D-48CC-A3B1-03FA589ECFBF}" name="PivotTable1" cacheId="4" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="1">
-  <location ref="A15:C26" firstHeaderRow="0" firstDataRow="1" firstDataCol="1" rowPageCount="1" colPageCount="1"/>
+  <location ref="A15:C22" firstHeaderRow="0" firstDataRow="1" firstDataCol="1" rowPageCount="1" colPageCount="1"/>
   <pivotFields count="4">
     <pivotField axis="axisRow" showAll="0">
       <items count="11">
@@ -2093,18 +2042,12 @@
   <rowFields count="1">
     <field x="0"/>
   </rowFields>
-  <rowItems count="11">
-    <i>
-      <x/>
-    </i>
+  <rowItems count="7">
     <i>
       <x v="1"/>
     </i>
     <i>
       <x v="2"/>
-    </i>
-    <i>
-      <x v="3"/>
     </i>
     <i>
       <x v="4"/>
@@ -2113,13 +2056,7 @@
       <x v="5"/>
     </i>
     <i>
-      <x v="6"/>
-    </i>
-    <i>
       <x v="7"/>
-    </i>
-    <i>
-      <x v="8"/>
     </i>
     <i>
       <x v="9"/>
@@ -2140,7 +2077,7 @@
     </i>
   </colItems>
   <pageFields count="1">
-    <pageField fld="1" hier="-1"/>
+    <pageField fld="1" item="0" hier="-1"/>
   </pageFields>
   <dataFields count="2">
     <dataField name="Sum of Hamburger" fld="2" baseField="0" baseItem="0" numFmtId="9"/>
@@ -4110,7 +4047,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8E7A7E49-887B-4928-B337-0FB9F6A85E81}">
-  <dimension ref="A1:D26"/>
+  <dimension ref="A1:D22"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="12.453125" bestFit="1" customWidth="1"/>
@@ -4297,7 +4234,7 @@
         <v>60</v>
       </c>
       <c r="B13" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.35">
@@ -4305,15 +4242,15 @@
         <v>63</v>
       </c>
       <c r="B15" t="s">
+        <v>65</v>
+      </c>
+      <c r="C15" t="s">
         <v>66</v>
-      </c>
-      <c r="C15" t="s">
-        <v>67</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A16" s="8" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="B16" s="1">
         <v>0.67</v>
@@ -4324,112 +4261,68 @@
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A17" s="8" t="s">
-        <v>22</v>
+        <v>36</v>
       </c>
       <c r="B17" s="1">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="C17" s="1">
-        <v>0.2</v>
+        <v>0.19</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A18" s="8" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B18" s="1">
-        <v>0.68</v>
+        <v>0.69</v>
       </c>
       <c r="C18" s="1">
-        <v>0.19</v>
+        <v>0.18</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A19" s="8" t="s">
-        <v>48</v>
+        <v>34</v>
       </c>
       <c r="B19" s="1">
-        <v>0.75</v>
+        <v>0.7</v>
       </c>
       <c r="C19" s="1">
-        <v>0.14000000000000001</v>
+        <v>0.18</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A20" s="8" t="s">
-        <v>35</v>
+        <v>44</v>
       </c>
       <c r="B20" s="1">
-        <v>0.69</v>
+        <v>0.75</v>
       </c>
       <c r="C20" s="1">
-        <v>0.18</v>
+        <v>0.14000000000000001</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A21" s="8" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="B21" s="1">
-        <v>0.7</v>
+        <v>0.66</v>
       </c>
       <c r="C21" s="1">
-        <v>0.18</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A22" s="8" t="s">
-        <v>41</v>
+        <v>64</v>
       </c>
       <c r="B22" s="1">
-        <v>0.69</v>
+        <v>4.1500000000000004</v>
       </c>
       <c r="C22" s="1">
-        <v>0.17</v>
-      </c>
-    </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A23" s="8" t="s">
-        <v>44</v>
-      </c>
-      <c r="B23" s="1">
-        <v>0.75</v>
-      </c>
-      <c r="C23" s="1">
-        <v>0.14000000000000001</v>
-      </c>
-    </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A24" s="8" t="s">
-        <v>43</v>
-      </c>
-      <c r="B24" s="1">
-        <v>0.68</v>
-      </c>
-      <c r="C24" s="1">
-        <v>0.18</v>
-      </c>
-    </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A25" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="B25" s="1">
-        <v>0.66</v>
-      </c>
-      <c r="C25" s="1">
-        <v>0.2</v>
-      </c>
-    </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A26" s="8" t="s">
-        <v>64</v>
-      </c>
-      <c r="B26" s="1">
-        <v>6.9399999999999995</v>
-      </c>
-      <c r="C26" s="1">
-        <v>1.7799999999999998</v>
+        <v>1.0900000000000001</v>
       </c>
     </row>
   </sheetData>
